--- a/tests/ExcelRenderer.Formulas.Tests/Fixtures/Oracle/Mapping/mapping-3.xlsx
+++ b/tests/ExcelRenderer.Formulas.Tests/Fixtures/Oracle/Mapping/mapping-3.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Invoice" sheetId="1" r:id="Reb1d0caf0f21458e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rates" sheetId="2" r:id="R7cbf4ce773394710"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master" sheetId="3" r:id="R4a772b39f6784db1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Invoice" sheetId="1" r:id="R78ee10b27516481e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rates" sheetId="2" r:id="R07134c24fb5d4f4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master" sheetId="3" r:id="Rccf89b2c9f214599"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="Amounts">'Invoice'!$D$1:$D$4</x:definedName>
